--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>3629.613692065931</v>
+        <v>2347.224404253075</v>
       </c>
       <c r="D6">
-        <v>276.4774555870436</v>
+        <v>182.9556301445923</v>
       </c>
       <c r="E6">
-        <v>4578.371663237075</v>
+        <v>73.16137126765993</v>
       </c>
       <c r="F6">
-        <v>1987.566796274164</v>
+        <v>4750.237302797428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,22 +518,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2529.569307391621</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>191.5269402468302</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>34.23615350539696</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5106.121412363852</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>2347.224404253075</v>
+        <v>3237.642755560177</v>
       </c>
       <c r="D8">
-        <v>182.9556301445923</v>
+        <v>260.9789878250358</v>
       </c>
       <c r="E8">
-        <v>73.16137126765993</v>
+        <v>-66.36838101779699</v>
       </c>
       <c r="F8">
-        <v>4750.237302797428</v>
+        <v>6016.77774961595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="C9">
-        <v>2529.569307391621</v>
+        <v>3222.915557927578</v>
       </c>
       <c r="D9">
-        <v>191.5269402468302</v>
+        <v>238.7480035513384</v>
       </c>
       <c r="E9">
-        <v>34.23615350539696</v>
+        <v>-45.8080836867474</v>
       </c>
       <c r="F9">
-        <v>5106.121412363852</v>
+        <v>5925.365518466964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -590,22 +590,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>3237.642755560177</v>
+        <v>2384.448403736423</v>
       </c>
       <c r="D10">
-        <v>260.9789878250358</v>
+        <v>303.0994159039039</v>
       </c>
       <c r="E10">
-        <v>-66.36838101779699</v>
+        <v>1718.398198899412</v>
       </c>
       <c r="F10">
-        <v>6016.77774961595</v>
+        <v>2981.24789460943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="C11">
-        <v>3222.915557927578</v>
+        <v>1190.702010578538</v>
       </c>
       <c r="D11">
-        <v>238.7480035513384</v>
+        <v>137.0433326068824</v>
       </c>
       <c r="E11">
-        <v>-45.8080836867474</v>
+        <v>858.7854577214898</v>
       </c>
       <c r="F11">
-        <v>5925.365518466964</v>
+        <v>1486.42548531547</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>2384.448403736423</v>
+        <v>132514.5131922857</v>
       </c>
       <c r="D12">
-        <v>303.0994159039039</v>
+        <v>9565.357379365007</v>
       </c>
       <c r="E12">
-        <v>1718.398198899412</v>
+        <v>98674.44200563467</v>
       </c>
       <c r="F12">
-        <v>2981.24789460943</v>
+        <v>160176.1595485081</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -662,22 +662,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>1190.702010578538</v>
+        <v>45862.4334559237</v>
       </c>
       <c r="D13">
-        <v>137.0433326068824</v>
+        <v>3487.525465558493</v>
       </c>
       <c r="E13">
-        <v>858.7854577214898</v>
+        <v>34205.12877766402</v>
       </c>
       <c r="F13">
-        <v>1486.42548531547</v>
+        <v>55395.18123943473</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -686,22 +686,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>132514.5131922857</v>
-      </c>
-      <c r="D14">
-        <v>9565.357379365007</v>
+        <v>145052.1826810451</v>
       </c>
       <c r="E14">
-        <v>98674.44200563467</v>
+        <v>103249.0972297795</v>
       </c>
       <c r="F14">
-        <v>160176.1595485081</v>
+        <v>180162.587578069</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -710,16 +707,55 @@
         </is>
       </c>
       <c r="C15">
-        <v>45862.4334559237</v>
-      </c>
-      <c r="D15">
-        <v>3487.525465558493</v>
+        <v>58772.68437891013</v>
       </c>
       <c r="E15">
-        <v>34205.12877766402</v>
+        <v>38888.8339547592</v>
       </c>
       <c r="F15">
-        <v>55395.18123943473</v>
+        <v>75926.15895163271</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>160989.0000632484</v>
+      </c>
+      <c r="E16">
+        <v>116714.4762517086</v>
+      </c>
+      <c r="F16">
+        <v>198398.4286353176</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>80493.25711837321</v>
+      </c>
+      <c r="E17">
+        <v>57319.5282197714</v>
+      </c>
+      <c r="F17">
+        <v>100704.9440874856</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,22 +367,62 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases</t>
+          <t>tot_cases_mid</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_se</t>
+          <t>tot_cases_low</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_low</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_up</t>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
@@ -401,13 +441,37 @@
         <v>15936.81738220334</v>
       </c>
       <c r="D2">
-        <v>1657.791408750476</v>
+        <v>13465.37902192904</v>
       </c>
       <c r="E2">
-        <v>13465.37902192904</v>
+        <v>18235.8410572486</v>
       </c>
       <c r="F2">
-        <v>18235.8410572486</v>
+        <v>28592.2402340249</v>
+      </c>
+      <c r="G2">
+        <v>24207.07799942461</v>
+      </c>
+      <c r="H2">
+        <v>32672.04512626504</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>3802767951.125311</v>
+      </c>
+      <c r="M2">
+        <v>3219541373.923473</v>
+      </c>
+      <c r="N2">
+        <v>4345382001.793251</v>
       </c>
     </row>
     <row r="3">
@@ -425,19 +489,43 @@
         <v>21720.57273946307</v>
       </c>
       <c r="D3">
-        <v>1961.307719038575</v>
+        <v>18430.69426501219</v>
       </c>
       <c r="E3">
-        <v>18430.69426501219</v>
+        <v>24778.78513585294</v>
       </c>
       <c r="F3">
-        <v>24778.78513585294</v>
+        <v>28956.00321587296</v>
+      </c>
+      <c r="G3">
+        <v>24681.27720300399</v>
+      </c>
+      <c r="H3">
+        <v>32934.56766132678</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>3851148427.711103</v>
+      </c>
+      <c r="M3">
+        <v>3282609867.99953</v>
+      </c>
+      <c r="N3">
+        <v>4380297498.956462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -446,22 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>4568.353925209686</v>
+        <v>777.3906568769762</v>
       </c>
       <c r="D4">
-        <v>415.3966729889607</v>
+        <v>22.40175943121739</v>
       </c>
       <c r="E4">
-        <v>2849.464034995572</v>
+        <v>1572.856985505977</v>
       </c>
       <c r="F4">
-        <v>6238.16508253809</v>
+        <v>205.4227740551028</v>
+      </c>
+      <c r="G4">
+        <v>3.840993288977415</v>
+      </c>
+      <c r="H4">
+        <v>525.5795513595959</v>
+      </c>
+      <c r="I4">
+        <v>34272821.88973517</v>
+      </c>
+      <c r="J4">
+        <v>987626.368044079</v>
+      </c>
+      <c r="K4">
+        <v>69342545.92000191</v>
+      </c>
+      <c r="L4">
+        <v>27321228.94932868</v>
+      </c>
+      <c r="M4">
+        <v>510852.1074339962</v>
+      </c>
+      <c r="N4">
+        <v>69902080.33082625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,22 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>5967.064047088697</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>460.5257894142127</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3836.491649555051</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>8013.065296051683</v>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -494,22 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>2347.224404253075</v>
+        <v>4568.353925209686</v>
       </c>
       <c r="D6">
-        <v>182.9556301445923</v>
+        <v>2849.464034995572</v>
       </c>
       <c r="E6">
-        <v>73.16137126765993</v>
+        <v>6238.16508253809</v>
       </c>
       <c r="F6">
-        <v>4750.237302797428</v>
+        <v>739.1413892267392</v>
+      </c>
+      <c r="G6">
+        <v>364.8571756365798</v>
+      </c>
+      <c r="H6">
+        <v>1223.379696474785</v>
+      </c>
+      <c r="I6">
+        <v>254466450.3420297</v>
+      </c>
+      <c r="J6">
+        <v>158720845.6773234</v>
+      </c>
+      <c r="K6">
+        <v>347478271.4275365</v>
+      </c>
+      <c r="L6">
+        <v>98305804.76715632</v>
+      </c>
+      <c r="M6">
+        <v>48526004.35966512</v>
+      </c>
+      <c r="N6">
+        <v>162709499.6311464</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,22 +678,46 @@
         </is>
       </c>
       <c r="C7">
-        <v>2529.569307391621</v>
+        <v>5967.064047088697</v>
       </c>
       <c r="D7">
-        <v>191.5269402468302</v>
+        <v>3836.491649555051</v>
       </c>
       <c r="E7">
-        <v>34.23615350539696</v>
+        <v>8013.065296051683</v>
       </c>
       <c r="F7">
-        <v>5106.121412363852</v>
+        <v>786.1821219842466</v>
+      </c>
+      <c r="G7">
+        <v>397.5199683396013</v>
+      </c>
+      <c r="H7">
+        <v>1284.445847413027</v>
+      </c>
+      <c r="I7">
+        <v>332377401.5509345</v>
+      </c>
+      <c r="J7">
+        <v>213700257.8635158</v>
+      </c>
+      <c r="K7">
+        <v>446343763.1206713</v>
+      </c>
+      <c r="L7">
+        <v>104562222.2239048</v>
+      </c>
+      <c r="M7">
+        <v>52870155.78916698</v>
+      </c>
+      <c r="N7">
+        <v>170831297.7059326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -542,22 +726,46 @@
         </is>
       </c>
       <c r="C8">
-        <v>3237.642755560177</v>
+        <v>2347.224404253075</v>
       </c>
       <c r="D8">
-        <v>260.9789878250358</v>
+        <v>73.16137126765993</v>
       </c>
       <c r="E8">
-        <v>-66.36838101779699</v>
+        <v>4750.237302797428</v>
       </c>
       <c r="F8">
-        <v>6016.77774961595</v>
+        <v>449.5890124044093</v>
+      </c>
+      <c r="G8">
+        <v>8.92133771922863</v>
+      </c>
+      <c r="H8">
+        <v>1049.986423188863</v>
+      </c>
+      <c r="I8">
+        <v>34755351.7537753</v>
+      </c>
+      <c r="J8">
+        <v>1083300.42436024</v>
+      </c>
+      <c r="K8">
+        <v>70336763.74252151</v>
+      </c>
+      <c r="L8">
+        <v>59795338.64978644</v>
+      </c>
+      <c r="M8">
+        <v>1186537.916657408</v>
+      </c>
+      <c r="N8">
+        <v>139648194.2841187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -566,22 +774,46 @@
         </is>
       </c>
       <c r="C9">
-        <v>3222.915557927578</v>
+        <v>2529.569307391621</v>
       </c>
       <c r="D9">
-        <v>238.7480035513384</v>
+        <v>34.23615350539696</v>
       </c>
       <c r="E9">
-        <v>-45.8080836867474</v>
+        <v>5106.121412363852</v>
       </c>
       <c r="F9">
-        <v>5925.365518466964</v>
+        <v>343.3374105484882</v>
+      </c>
+      <c r="G9">
+        <v>3.280060594898655</v>
+      </c>
+      <c r="H9">
+        <v>800.4912417719837</v>
+      </c>
+      <c r="I9">
+        <v>37455332.73454773</v>
+      </c>
+      <c r="J9">
+        <v>506934.7249544119</v>
+      </c>
+      <c r="K9">
+        <v>75606339.75287163</v>
+      </c>
+      <c r="L9">
+        <v>45663875.60294893</v>
+      </c>
+      <c r="M9">
+        <v>436248.0591215211</v>
+      </c>
+      <c r="N9">
+        <v>106465335.1556738</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -590,22 +822,46 @@
         </is>
       </c>
       <c r="C10">
-        <v>2384.448403736423</v>
+        <v>3237.642755560177</v>
       </c>
       <c r="D10">
-        <v>303.0994159039039</v>
+        <v>-66.36838101779699</v>
       </c>
       <c r="E10">
-        <v>1718.398198899412</v>
+        <v>6016.77774961595</v>
       </c>
       <c r="F10">
-        <v>2981.24789460943</v>
+        <v>862.9829262299427</v>
+      </c>
+      <c r="G10">
+        <v>-12.33997752082171</v>
+      </c>
+      <c r="H10">
+        <v>2031.924478019441</v>
+      </c>
+      <c r="I10">
+        <v>243473972.8608811</v>
+      </c>
+      <c r="J10">
+        <v>-4990968.62091934</v>
+      </c>
+      <c r="K10">
+        <v>452467703.5488692</v>
+      </c>
+      <c r="L10">
+        <v>114776729.1885824</v>
+      </c>
+      <c r="M10">
+        <v>-1641217.010269287</v>
+      </c>
+      <c r="N10">
+        <v>270245955.5765857</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,22 +870,46 @@
         </is>
       </c>
       <c r="C11">
-        <v>1190.702010578538</v>
+        <v>3222.915557927578</v>
       </c>
       <c r="D11">
-        <v>137.0433326068824</v>
+        <v>-45.8080836867474</v>
       </c>
       <c r="E11">
-        <v>858.7854577214898</v>
+        <v>5925.365518466964</v>
       </c>
       <c r="F11">
-        <v>1486.42548531547</v>
+        <v>632.9623310563684</v>
+      </c>
+      <c r="G11">
+        <v>-7.065500841420956</v>
+      </c>
+      <c r="H11">
+        <v>1479.682271232525</v>
+      </c>
+      <c r="I11">
+        <v>242366472.8717118</v>
+      </c>
+      <c r="J11">
+        <v>-3444813.701327092</v>
+      </c>
+      <c r="K11">
+        <v>445593412.3542344</v>
+      </c>
+      <c r="L11">
+        <v>84183990.030497</v>
+      </c>
+      <c r="M11">
+        <v>-939711.6119089872</v>
+      </c>
+      <c r="N11">
+        <v>196797742.0739258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -638,22 +918,46 @@
         </is>
       </c>
       <c r="C12">
-        <v>132514.5131922857</v>
+        <v>2384.448403736423</v>
       </c>
       <c r="D12">
-        <v>9565.357379365007</v>
+        <v>1718.398198899412</v>
       </c>
       <c r="E12">
-        <v>98674.44200563467</v>
+        <v>2981.24789460943</v>
       </c>
       <c r="F12">
-        <v>160176.1595485081</v>
+        <v>636.4554083743607</v>
+      </c>
+      <c r="G12">
+        <v>368.1618173958173</v>
+      </c>
+      <c r="H12">
+        <v>904.9242175441377</v>
+      </c>
+      <c r="I12">
+        <v>40151726.67051771</v>
+      </c>
+      <c r="J12">
+        <v>28936107.27126723</v>
+      </c>
+      <c r="K12">
+        <v>50201233.29732811</v>
+      </c>
+      <c r="L12">
+        <v>84648569.31378996</v>
+      </c>
+      <c r="M12">
+        <v>48965521.7136437</v>
+      </c>
+      <c r="N12">
+        <v>120354920.9333703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -662,22 +966,46 @@
         </is>
       </c>
       <c r="C13">
-        <v>45862.4334559237</v>
+        <v>1190.702010578538</v>
       </c>
       <c r="D13">
-        <v>3487.525465558493</v>
+        <v>858.7854577214898</v>
       </c>
       <c r="E13">
-        <v>34205.12877766402</v>
+        <v>1486.42548531547</v>
       </c>
       <c r="F13">
-        <v>55395.18123943473</v>
+        <v>158.6886770578006</v>
+      </c>
+      <c r="G13">
+        <v>92.24176815624003</v>
+      </c>
+      <c r="H13">
+        <v>224.6571567232756</v>
+      </c>
+      <c r="I13">
+        <v>20050231.15613202</v>
+      </c>
+      <c r="J13">
+        <v>14461088.32257216</v>
+      </c>
+      <c r="K13">
+        <v>25029918.74722721</v>
+      </c>
+      <c r="L13">
+        <v>21105594.04868748</v>
+      </c>
+      <c r="M13">
+        <v>12268155.16477992</v>
+      </c>
+      <c r="N13">
+        <v>29879401.84419566</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -686,19 +1014,46 @@
         </is>
       </c>
       <c r="C14">
-        <v>145052.1826810451</v>
+        <v>132514.5131922857</v>
+      </c>
+      <c r="D14">
+        <v>98674.44200563467</v>
       </c>
       <c r="E14">
-        <v>103249.0972297795</v>
+        <v>160176.1595485081</v>
       </c>
       <c r="F14">
-        <v>180162.587578069</v>
+        <v>150358.5827161974</v>
+      </c>
+      <c r="G14">
+        <v>69234.75185318149</v>
+      </c>
+      <c r="H14">
+        <v>277751.6065853683</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>19997691501.25425</v>
+      </c>
+      <c r="M14">
+        <v>9208221996.473137</v>
+      </c>
+      <c r="N14">
+        <v>36940963675.85399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -707,55 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>58772.68437891013</v>
+        <v>45862.4334559237</v>
+      </c>
+      <c r="D15">
+        <v>34205.12877766402</v>
       </c>
       <c r="E15">
-        <v>38888.8339547592</v>
+        <v>55395.18123943473</v>
       </c>
       <c r="F15">
-        <v>75926.15895163271</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>160989.0000632484</v>
-      </c>
-      <c r="E16">
-        <v>116714.4762517086</v>
-      </c>
-      <c r="F16">
-        <v>198398.4286353176</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>80493.25711837321</v>
-      </c>
-      <c r="E17">
-        <v>57319.5282197714</v>
-      </c>
-      <c r="F17">
-        <v>100704.9440874856</v>
+        <v>45689.63899675892</v>
+      </c>
+      <c r="G15">
+        <v>21039.32351696153</v>
+      </c>
+      <c r="H15">
+        <v>84384.72086729162</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>6076721986.568936</v>
+      </c>
+      <c r="M15">
+        <v>2798230027.755883</v>
+      </c>
+      <c r="N15">
+        <v>11223167875.34978</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>777.3906568769762</v>
+        <v>830.3701511487852</v>
       </c>
       <c r="D4">
-        <v>22.40175943121739</v>
+        <v>23.96606678829604</v>
       </c>
       <c r="E4">
-        <v>1572.856985505977</v>
+        <v>1679.989000054051</v>
       </c>
       <c r="F4">
-        <v>205.4227740551028</v>
+        <v>218.1251200341125</v>
       </c>
       <c r="G4">
-        <v>3.840993288977415</v>
+        <v>4.107719637279583</v>
       </c>
       <c r="H4">
-        <v>525.5795513595959</v>
+        <v>558.0467703075753</v>
       </c>
       <c r="I4">
-        <v>34272821.88973517</v>
+        <v>36608528.85369654</v>
       </c>
       <c r="J4">
-        <v>987626.368044079</v>
+        <v>1056591.986495604</v>
       </c>
       <c r="K4">
-        <v>69342545.92000191</v>
+        <v>74065675.04538301</v>
       </c>
       <c r="L4">
-        <v>27321228.94932868</v>
+        <v>29010640.96453696</v>
       </c>
       <c r="M4">
-        <v>510852.1074339962</v>
+        <v>546326.7117581846</v>
       </c>
       <c r="N4">
-        <v>69902080.33082625</v>
+        <v>74220220.45090751</v>
       </c>
     </row>
     <row r="5">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>4568.353925209686</v>
+        <v>12451.16645341587</v>
       </c>
       <c r="D6">
-        <v>2849.464034995572</v>
+        <v>7769.141426128057</v>
       </c>
       <c r="E6">
-        <v>6238.16508253809</v>
+        <v>16996.05159522851</v>
       </c>
       <c r="F6">
-        <v>739.1413892267392</v>
+        <v>1941.523584318884</v>
       </c>
       <c r="G6">
-        <v>364.8571756365798</v>
+        <v>958.8599264275309</v>
       </c>
       <c r="H6">
-        <v>1223.379696474785</v>
+        <v>3211.797140461129</v>
       </c>
       <c r="I6">
-        <v>254466450.3420297</v>
+        <v>693554873.7881713</v>
       </c>
       <c r="J6">
-        <v>158720845.6773234</v>
+        <v>432756715.7181846</v>
       </c>
       <c r="K6">
-        <v>347478271.4275365</v>
+        <v>946714065.9574171</v>
       </c>
       <c r="L6">
-        <v>98305804.76715632</v>
+        <v>258222636.7144116</v>
       </c>
       <c r="M6">
-        <v>48526004.35966512</v>
+        <v>127528370.2148616</v>
       </c>
       <c r="N6">
-        <v>162709499.6311464</v>
+        <v>427169019.6813302</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>5967.064047088697</v>
+        <v>13770.2100899151</v>
       </c>
       <c r="D7">
-        <v>3836.491649555051</v>
+        <v>8846.247302135826</v>
       </c>
       <c r="E7">
-        <v>8013.065296051683</v>
+        <v>18503.50329710171</v>
       </c>
       <c r="F7">
-        <v>786.1821219842466</v>
+        <v>1590.615778847993</v>
       </c>
       <c r="G7">
-        <v>397.5199683396013</v>
+        <v>805.0283972465458</v>
       </c>
       <c r="H7">
-        <v>1284.445847413027</v>
+        <v>2596.879168300507</v>
       </c>
       <c r="I7">
-        <v>332377401.5509345</v>
+        <v>767028242.4284511</v>
       </c>
       <c r="J7">
-        <v>213700257.8635158</v>
+        <v>492753667.2235696</v>
       </c>
       <c r="K7">
-        <v>446343763.1206713</v>
+        <v>1030682140.655158</v>
       </c>
       <c r="L7">
-        <v>104562222.2239048</v>
+        <v>211551898.586783</v>
       </c>
       <c r="M7">
-        <v>52870155.78916698</v>
+        <v>107068776.8337906</v>
       </c>
       <c r="N7">
-        <v>170831297.7059326</v>
+        <v>345384929.3839675</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>2347.224404253075</v>
+        <v>12608.35094939108</v>
       </c>
       <c r="D8">
-        <v>73.16137126765993</v>
+        <v>341.5126919798212</v>
       </c>
       <c r="E8">
-        <v>4750.237302797428</v>
+        <v>25503.27169059733</v>
       </c>
       <c r="F8">
-        <v>449.5890124044093</v>
+        <v>3597.011972976959</v>
       </c>
       <c r="G8">
-        <v>8.92133771922863</v>
+        <v>72.0527039690197</v>
       </c>
       <c r="H8">
-        <v>1049.986423188863</v>
+        <v>8398.947917194482</v>
       </c>
       <c r="I8">
-        <v>34755351.7537753</v>
+        <v>186691852.5076337</v>
       </c>
       <c r="J8">
-        <v>1083300.42436024</v>
+        <v>5056778.43014523</v>
       </c>
       <c r="K8">
-        <v>70336763.74252151</v>
+        <v>377626943.9226753</v>
       </c>
       <c r="L8">
-        <v>59795338.64978644</v>
+        <v>478402592.4059356</v>
       </c>
       <c r="M8">
-        <v>1186537.916657408</v>
+        <v>9583009.62787962</v>
       </c>
       <c r="N8">
-        <v>139648194.2841187</v>
+        <v>1117060072.986866</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>2529.569307391621</v>
+        <v>7280.920694582312</v>
       </c>
       <c r="D9">
-        <v>34.23615350539696</v>
+        <v>113.2657565906829</v>
       </c>
       <c r="E9">
-        <v>5106.121412363852</v>
+        <v>14697.12783036198</v>
       </c>
       <c r="F9">
-        <v>343.3374105484882</v>
+        <v>1076.400255575184</v>
       </c>
       <c r="G9">
-        <v>3.280060594898655</v>
+        <v>13.75343852158111</v>
       </c>
       <c r="H9">
-        <v>800.4912417719837</v>
+        <v>2509.739008195952</v>
       </c>
       <c r="I9">
-        <v>37455332.73454773</v>
+        <v>107808592.7246803</v>
       </c>
       <c r="J9">
-        <v>506934.7249544119</v>
+        <v>1677126.057838241</v>
       </c>
       <c r="K9">
-        <v>75606339.75287163</v>
+        <v>217620371.78417</v>
       </c>
       <c r="L9">
-        <v>45663875.60294893</v>
+        <v>143161233.9914995</v>
       </c>
       <c r="M9">
-        <v>436248.0591215211</v>
+        <v>1829207.323370288</v>
       </c>
       <c r="N9">
-        <v>106465335.1556738</v>
+        <v>333795288.0900615</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>3237.642755560177</v>
+        <v>2004.309455944744</v>
       </c>
       <c r="D10">
-        <v>-66.36838101779699</v>
+        <v>-38.22584290513367</v>
       </c>
       <c r="E10">
-        <v>6016.77774961595</v>
+        <v>3716.711599418889</v>
       </c>
       <c r="F10">
-        <v>862.9829262299427</v>
+        <v>671.3461051168656</v>
       </c>
       <c r="G10">
-        <v>-12.33997752082171</v>
+        <v>-9.529064761315126</v>
       </c>
       <c r="H10">
-        <v>2031.924478019441</v>
+        <v>1580.452775246205</v>
       </c>
       <c r="I10">
-        <v>243473972.8608811</v>
+        <v>150726075.3965008</v>
       </c>
       <c r="J10">
-        <v>-4990968.62091934</v>
+        <v>-2874621.612308952</v>
       </c>
       <c r="K10">
-        <v>452467703.5488692</v>
+        <v>279500428.9879004</v>
       </c>
       <c r="L10">
-        <v>114776729.1885824</v>
+        <v>89289031.98054312</v>
       </c>
       <c r="M10">
-        <v>-1641217.010269287</v>
+        <v>-1267365.613254912</v>
       </c>
       <c r="N10">
-        <v>270245955.5765857</v>
+        <v>210200219.1077453</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>3222.915557927578</v>
+        <v>2148.040713968812</v>
       </c>
       <c r="D11">
-        <v>-45.8080836867474</v>
+        <v>-31.63323760894794</v>
       </c>
       <c r="E11">
-        <v>5925.365518466964</v>
+        <v>3953.733148619258</v>
       </c>
       <c r="F11">
-        <v>632.9623310563684</v>
+        <v>612.4907278556932</v>
       </c>
       <c r="G11">
-        <v>-7.065500841420956</v>
+        <v>-7.680382973848277</v>
       </c>
       <c r="H11">
-        <v>1479.682271232525</v>
+        <v>1436.537461637133</v>
       </c>
       <c r="I11">
-        <v>242366472.8717118</v>
+        <v>161534809.7311683</v>
       </c>
       <c r="J11">
-        <v>-3444813.701327092</v>
+        <v>-2378851.101430498</v>
       </c>
       <c r="K11">
-        <v>445593412.3542344</v>
+        <v>297324686.5093169</v>
       </c>
       <c r="L11">
-        <v>84183990.030497</v>
+        <v>81461266.8048072</v>
       </c>
       <c r="M11">
-        <v>-939711.6119089872</v>
+        <v>-1021490.935521821</v>
       </c>
       <c r="N11">
-        <v>196797742.0739258</v>
+        <v>191059482.3977386</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>2384.448403736423</v>
+        <v>5704.556738423242</v>
       </c>
       <c r="D12">
-        <v>1718.398198899412</v>
+        <v>4110.358339865177</v>
       </c>
       <c r="E12">
-        <v>2981.24789460943</v>
+        <v>7131.222289336152</v>
       </c>
       <c r="F12">
-        <v>636.4554083743607</v>
+        <v>1696.011621456228</v>
       </c>
       <c r="G12">
-        <v>368.1618173958173</v>
+        <v>981.3754516187024</v>
       </c>
       <c r="H12">
-        <v>904.9242175441377</v>
+        <v>2409.694859134266</v>
       </c>
       <c r="I12">
-        <v>40151726.67051771</v>
+        <v>96059030.91830906</v>
       </c>
       <c r="J12">
-        <v>28936107.27126723</v>
+        <v>69214324.08498967</v>
       </c>
       <c r="K12">
-        <v>50201233.29732811</v>
+        <v>120082652.1301314</v>
       </c>
       <c r="L12">
-        <v>84648569.31378996</v>
+        <v>225569545.6536784</v>
       </c>
       <c r="M12">
-        <v>48965521.7136437</v>
+        <v>130522935.0652874</v>
       </c>
       <c r="N12">
-        <v>120354920.9333703</v>
+        <v>320489416.2648574</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>1190.702010578538</v>
+        <v>3638.22705415106</v>
       </c>
       <c r="D13">
-        <v>858.7854577214898</v>
+        <v>2627.225361846554</v>
       </c>
       <c r="E13">
-        <v>1486.42548531547</v>
+        <v>4538.771809711213</v>
       </c>
       <c r="F13">
-        <v>158.6886770578006</v>
+        <v>555.135456549922</v>
       </c>
       <c r="G13">
-        <v>92.24176815624003</v>
+        <v>323.2138405875617</v>
       </c>
       <c r="H13">
-        <v>224.6571567232756</v>
+        <v>785.0259857140907</v>
       </c>
       <c r="I13">
-        <v>20050231.15613202</v>
+        <v>61264105.36484969</v>
       </c>
       <c r="J13">
-        <v>14461088.32257216</v>
+        <v>44239847.86813409</v>
       </c>
       <c r="K13">
-        <v>25029918.74722721</v>
+        <v>76428378.50372709</v>
       </c>
       <c r="L13">
-        <v>21105594.04868748</v>
+        <v>73833015.72113962</v>
       </c>
       <c r="M13">
-        <v>12268155.16477992</v>
+        <v>42987440.7981457</v>
       </c>
       <c r="N13">
-        <v>29879401.84419566</v>
+        <v>104408456.0999741</v>
       </c>
     </row>
     <row r="14">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>132514.5131922857</v>
+        <v>67587.25211501982</v>
       </c>
       <c r="D14">
-        <v>98674.44200563467</v>
+        <v>50266.75700739733</v>
       </c>
       <c r="E14">
-        <v>160176.1595485081</v>
+        <v>81736.21956205854</v>
       </c>
       <c r="F14">
-        <v>150358.5827161974</v>
+        <v>64401.94708783021</v>
       </c>
       <c r="G14">
-        <v>69234.75185318149</v>
+        <v>29650.5062572388</v>
       </c>
       <c r="H14">
-        <v>277751.6065853683</v>
+        <v>118972.1819007881</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>19997691501.25425</v>
+        <v>8565458962.681417</v>
       </c>
       <c r="M14">
-        <v>9208221996.473137</v>
+        <v>3943517332.21276</v>
       </c>
       <c r="N14">
-        <v>36940963675.85399</v>
+        <v>15823300192.80481</v>
       </c>
     </row>
     <row r="15">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>45862.4334559237</v>
+        <v>27318.78515242044</v>
       </c>
       <c r="D15">
-        <v>34205.12877766402</v>
+        <v>20406.04303923879</v>
       </c>
       <c r="E15">
-        <v>55395.18123943473</v>
+        <v>32984.48756594546</v>
       </c>
       <c r="F15">
-        <v>45689.63899675892</v>
+        <v>20856.25373275864</v>
       </c>
       <c r="G15">
-        <v>21039.32351696153</v>
+        <v>9613.8571875216</v>
       </c>
       <c r="H15">
-        <v>84384.72086729162</v>
+        <v>38506.48210546467</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6076721986.568936</v>
+        <v>2773881746.4569</v>
       </c>
       <c r="M15">
-        <v>2798230027.755883</v>
+        <v>1278643005.940373</v>
       </c>
       <c r="N15">
-        <v>11223167875.34978</v>
+        <v>5121362120.026802</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>20463.37727576628</v>
+        <v>24600.95049746287</v>
       </c>
       <c r="D2">
-        <v>17839.15714927057</v>
+        <v>21089.5996061323</v>
       </c>
       <c r="E2">
-        <v>22935.94642871688</v>
+        <v>27886.51173331669</v>
       </c>
       <c r="F2">
-        <v>42427.10848102062</v>
+        <v>47998.56044319943</v>
       </c>
       <c r="G2">
-        <v>36803.44741484391</v>
+        <v>41293.01876841089</v>
       </c>
       <c r="H2">
-        <v>47714.72497980547</v>
+        <v>54281.36154998886</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5642805427.975742</v>
+        <v>6383808538.945524</v>
       </c>
       <c r="M2">
-        <v>4894858506.17424</v>
+        <v>5491971496.198648</v>
       </c>
       <c r="N2">
-        <v>6346058422.314127</v>
+        <v>7219421086.148519</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>30626.34298344658</v>
+        <v>34207.77804873243</v>
       </c>
       <c r="D3">
-        <v>26777.12365205432</v>
+        <v>29593.57874547202</v>
       </c>
       <c r="E3">
-        <v>34254.76814126071</v>
+        <v>38536.21438536532</v>
       </c>
       <c r="F3">
-        <v>49488.9923349814</v>
+        <v>53346.97483971681</v>
       </c>
       <c r="G3">
-        <v>43131.10785819954</v>
+        <v>46119.66778995514</v>
       </c>
       <c r="H3">
-        <v>55475.14622220814</v>
+        <v>60125.7675714435</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6582035980.552526</v>
+        <v>7095147653.682336</v>
       </c>
       <c r="M3">
-        <v>5736437345.140538</v>
+        <v>6133915816.064034</v>
       </c>
       <c r="N3">
-        <v>7378194447.553682</v>
+        <v>7996727087.001986</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>1056.137328627854</v>
+        <v>1248.612815553223</v>
       </c>
       <c r="D4">
-        <v>60.93005378622075</v>
+        <v>61.29332648930076</v>
       </c>
       <c r="E4">
-        <v>2137.570231094892</v>
+        <v>2528.160142138328</v>
       </c>
       <c r="F4">
-        <v>296.6374997337918</v>
+        <v>343.1225477244411</v>
       </c>
       <c r="G4">
-        <v>12.49731954080242</v>
+        <v>12.06727726724682</v>
       </c>
       <c r="H4">
-        <v>759.7616819675889</v>
+        <v>878.8530461058352</v>
       </c>
       <c r="I4">
-        <v>46561926.40721618</v>
+        <v>55047593.19929488</v>
       </c>
       <c r="J4">
-        <v>2686223.281273113</v>
+        <v>2702238.884933811</v>
       </c>
       <c r="K4">
-        <v>94239058.77828044</v>
+        <v>111458996.1864522</v>
       </c>
       <c r="L4">
-        <v>39452787.46459431</v>
+        <v>45635298.84735067</v>
       </c>
       <c r="M4">
-        <v>1662143.498926722</v>
+        <v>1604947.876543826</v>
       </c>
       <c r="N4">
-        <v>101048303.7016893</v>
+        <v>116887455.1320761</v>
       </c>
     </row>
     <row r="5">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>15383.96516907883</v>
+        <v>18574.73159296868</v>
       </c>
       <c r="D6">
-        <v>9729.106214531717</v>
+        <v>11620.21651129571</v>
       </c>
       <c r="E6">
-        <v>21012.33021416543</v>
+        <v>25438.54197189181</v>
       </c>
       <c r="F6">
-        <v>2608.850401091059</v>
+        <v>3037.993426880372</v>
       </c>
       <c r="G6">
-        <v>1295.531407004186</v>
+        <v>1501.497164350438</v>
       </c>
       <c r="H6">
-        <v>4336.190675191231</v>
+        <v>5049.096837717301</v>
       </c>
       <c r="I6">
-        <v>856917627.8480296</v>
+        <v>1034649699.191539</v>
       </c>
       <c r="J6">
-        <v>541930674.3618448</v>
+        <v>647269300.1121955</v>
       </c>
       <c r="K6">
-        <v>1170428817.589441</v>
+        <v>1416977664.91832</v>
       </c>
       <c r="L6">
-        <v>346977103.3451108</v>
+        <v>404053125.7750894</v>
       </c>
       <c r="M6">
-        <v>172305677.1315567</v>
+        <v>199699122.8586083</v>
       </c>
       <c r="N6">
-        <v>576713359.8004338</v>
+        <v>671529879.416401</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>18924.58206323431</v>
+        <v>21083.53521120251</v>
       </c>
       <c r="D7">
-        <v>12240.19728977783</v>
+        <v>13511.51035665206</v>
       </c>
       <c r="E7">
-        <v>25508.5598964714</v>
+        <v>28536.52674465354</v>
       </c>
       <c r="F7">
-        <v>2449.278510133241</v>
+        <v>2674.884376383136</v>
       </c>
       <c r="G7">
-        <v>1235.529511782479</v>
+        <v>1340.770409938568</v>
       </c>
       <c r="H7">
-        <v>4037.717336358473</v>
+        <v>4419.879214345772</v>
       </c>
       <c r="I7">
-        <v>1054137070.086274</v>
+        <v>1174395078.3344</v>
       </c>
       <c r="J7">
-        <v>681803469.4352047</v>
+        <v>752618149.88623</v>
       </c>
       <c r="K7">
-        <v>1420877803.353252</v>
+        <v>1589541612.730696</v>
       </c>
       <c r="L7">
-        <v>325754041.847721</v>
+        <v>355759622.0589571</v>
       </c>
       <c r="M7">
-        <v>164325425.0670697</v>
+        <v>178322464.5218296</v>
       </c>
       <c r="N7">
-        <v>537016405.735677</v>
+        <v>587843935.5079877</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>16858.19507946101</v>
+        <v>19639.00221098947</v>
       </c>
       <c r="D8">
-        <v>968.5030714048276</v>
+        <v>945.2686101049807</v>
       </c>
       <c r="E8">
-        <v>34126.387302877</v>
+        <v>39758.20605733652</v>
       </c>
       <c r="F8">
-        <v>5081.885991941673</v>
+        <v>5833.252709146847</v>
       </c>
       <c r="G8">
-        <v>230.7139602646996</v>
+        <v>218.6952994278149</v>
       </c>
       <c r="H8">
-        <v>11880.59426371095</v>
+        <v>13633.68166075154</v>
       </c>
       <c r="I8">
-        <v>249619294.5415795</v>
+        <v>290794705.7381204</v>
       </c>
       <c r="J8">
-        <v>14340624.97829131</v>
+        <v>13996592.30982444</v>
       </c>
       <c r="K8">
-        <v>505309416.7937</v>
+        <v>588699757.0909815</v>
       </c>
       <c r="L8">
-        <v>675890836.9282424</v>
+        <v>775822610.3165307</v>
       </c>
       <c r="M8">
-        <v>30684956.71520505</v>
+        <v>29086474.82389938</v>
       </c>
       <c r="N8">
-        <v>1580119037.073557</v>
+        <v>1813279660.879955</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>9883.273492018528</v>
+        <v>10911.63767997198</v>
       </c>
       <c r="D9">
-        <v>430.6174092848853</v>
+        <v>460.823121919975</v>
       </c>
       <c r="E9">
-        <v>19969.78102191763</v>
+        <v>22052.50879113228</v>
       </c>
       <c r="F9">
-        <v>1605.827569576263</v>
+        <v>1751.305584291346</v>
       </c>
       <c r="G9">
-        <v>63.63047340282968</v>
+        <v>65.54167383976392</v>
       </c>
       <c r="H9">
-        <v>3749.028387782099</v>
+        <v>4089.151541098824</v>
       </c>
       <c r="I9">
-        <v>146341630.5963185</v>
+        <v>161568619.1273454</v>
       </c>
       <c r="J9">
-        <v>6376151.979281288</v>
+        <v>6823407.966269104</v>
       </c>
       <c r="K9">
-        <v>295692547.5915344</v>
+        <v>326531497.6702951</v>
       </c>
       <c r="L9">
-        <v>213575066.753643</v>
+        <v>232923642.710749</v>
       </c>
       <c r="M9">
-        <v>8462852.962576346</v>
+        <v>8717042.6206886</v>
       </c>
       <c r="N9">
-        <v>498620775.5750192</v>
+        <v>543857154.9661436</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>2642.136597655282</v>
+        <v>3079.152031990513</v>
       </c>
       <c r="D10">
-        <v>-77.87279016837056</v>
+        <v>-81.5652831526404</v>
       </c>
       <c r="E10">
-        <v>4972.018462066192</v>
+        <v>5771.468572331606</v>
       </c>
       <c r="F10">
-        <v>925.637814197223</v>
+        <v>1068.008695612565</v>
       </c>
       <c r="G10">
-        <v>-20.62662228924829</v>
+        <v>-21.25571365630943</v>
       </c>
       <c r="H10">
-        <v>2212.889833086415</v>
+        <v>2542.199206471206</v>
       </c>
       <c r="I10">
-        <v>198691314.2802759</v>
+        <v>231555311.9577184</v>
       </c>
       <c r="J10">
-        <v>-5856111.693451637</v>
+        <v>-6133790.858361734</v>
       </c>
       <c r="K10">
-        <v>373900760.3658389</v>
+        <v>434020208.1079093</v>
       </c>
       <c r="L10">
-        <v>123109829.2882307</v>
+        <v>142045156.5164712</v>
       </c>
       <c r="M10">
-        <v>-2743340.764470023</v>
+        <v>-2827009.916289154</v>
       </c>
       <c r="N10">
-        <v>294314347.8004932</v>
+        <v>338112494.4606704</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>3126.192653741073</v>
+        <v>3415.492903387784</v>
       </c>
       <c r="D11">
-        <v>-82.81853487150974</v>
+        <v>-87.66933312498075</v>
       </c>
       <c r="E11">
-        <v>5853.129936103274</v>
+        <v>6389.26496163765</v>
       </c>
       <c r="F11">
-        <v>942.3777145710344</v>
+        <v>1023.195334391456</v>
       </c>
       <c r="G11">
-        <v>-20.12635281937332</v>
+        <v>-21.22088599622311</v>
       </c>
       <c r="H11">
-        <v>2247.647243689126</v>
+        <v>2438.594489967799</v>
       </c>
       <c r="I11">
-        <v>235092813.753983</v>
+        <v>256848481.8276645</v>
       </c>
       <c r="J11">
-        <v>-6228036.640872399</v>
+        <v>-6592821.520331657</v>
       </c>
       <c r="K11">
-        <v>440161224.3249021</v>
+        <v>480479114.3801115</v>
       </c>
       <c r="L11">
-        <v>125336236.0379476</v>
+        <v>136084979.4740637</v>
       </c>
       <c r="M11">
-        <v>-2676804.924976652</v>
+        <v>-2822377.837497673</v>
       </c>
       <c r="N11">
-        <v>298937083.4106537</v>
+        <v>324333067.1657173</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>6641.564563772612</v>
+        <v>8289.94422304287</v>
       </c>
       <c r="D12">
-        <v>4882.497576891242</v>
+        <v>6022.233564455917</v>
       </c>
       <c r="E12">
-        <v>8227.84256480152</v>
+        <v>10331.62833484003</v>
       </c>
       <c r="F12">
-        <v>2132.819125074505</v>
+        <v>2548.436607677986</v>
       </c>
       <c r="G12">
-        <v>1254.280771533119</v>
+        <v>1487.62148773283</v>
       </c>
       <c r="H12">
-        <v>3011.043133444895</v>
+        <v>3609.770460304351</v>
       </c>
       <c r="I12">
-        <v>111837305.6893671</v>
+        <v>139594370.7718183</v>
       </c>
       <c r="J12">
-        <v>82216376.69727169</v>
+        <v>101408390.9918734</v>
       </c>
       <c r="K12">
-        <v>138548640.9486931</v>
+        <v>173974289.5303712</v>
       </c>
       <c r="L12">
-        <v>283664943.6349092</v>
+        <v>338942068.8211722</v>
       </c>
       <c r="M12">
-        <v>166819342.6139049</v>
+        <v>197853657.8684663</v>
       </c>
       <c r="N12">
-        <v>400468736.748171</v>
+        <v>480099471.2204787</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>4576.554136217234</v>
+        <v>5199.494302381868</v>
       </c>
       <c r="D13">
-        <v>3376.343359734056</v>
+        <v>3806.472494643124</v>
       </c>
       <c r="E13">
-        <v>5652.314640183135</v>
+        <v>6449.432056470911</v>
       </c>
       <c r="F13">
-        <v>814.8941547572032</v>
+        <v>899.9388598911455</v>
       </c>
       <c r="G13">
-        <v>481.645246711073</v>
+        <v>528.6606014376198</v>
       </c>
       <c r="H13">
-        <v>1146.226008474122</v>
+        <v>1269.828127184036</v>
       </c>
       <c r="I13">
-        <v>77064595.09976205</v>
+        <v>87554284.55780822</v>
       </c>
       <c r="J13">
-        <v>56854245.83456183</v>
+        <v>64097190.33729566</v>
       </c>
       <c r="K13">
-        <v>95179326.22604367</v>
+        <v>108601986.3989135</v>
       </c>
       <c r="L13">
-        <v>108380922.582708</v>
+        <v>119691868.3655224</v>
       </c>
       <c r="M13">
-        <v>64058817.8125727</v>
+        <v>70311859.99120343</v>
       </c>
       <c r="N13">
-        <v>152448059.1270582</v>
+        <v>168887140.9154768</v>
       </c>
     </row>
     <row r="14">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>92391.10129139503</v>
+        <v>107153.1553122108</v>
       </c>
       <c r="D14">
-        <v>68149.3824924478</v>
+        <v>79218.0166650977</v>
       </c>
       <c r="E14">
-        <v>112201.2114600035</v>
+        <v>129974.2989825751</v>
       </c>
       <c r="F14">
-        <v>93347.60397074536</v>
+        <v>106609.7683464787</v>
       </c>
       <c r="G14">
-        <v>42585.42333967579</v>
+        <v>48775.23468282799</v>
       </c>
       <c r="H14">
-        <v>173232.1351216731</v>
+        <v>197573.4340998212</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>12415231328.10913</v>
+        <v>14179099190.08167</v>
       </c>
       <c r="M14">
-        <v>5663861304.17688</v>
+        <v>6487106212.816123</v>
       </c>
       <c r="N14">
-        <v>23039873971.18252</v>
+        <v>26277266735.27622</v>
       </c>
     </row>
     <row r="15">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>41143.17264924842</v>
+        <v>44955.61251605048</v>
       </c>
       <c r="D15">
-        <v>30468.78972813642</v>
+        <v>33286.7661588011</v>
       </c>
       <c r="E15">
-        <v>49894.55891095103</v>
+        <v>54504.37393346629</v>
       </c>
       <c r="F15">
-        <v>34320.43084678711</v>
+        <v>37220.15216527147</v>
       </c>
       <c r="G15">
-        <v>15690.58497143784</v>
+        <v>17012.15875473523</v>
       </c>
       <c r="H15">
-        <v>63652.74337423702</v>
+        <v>69011.83349335754</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>4564617302.622685</v>
+        <v>4950280237.981105</v>
       </c>
       <c r="M15">
-        <v>2086847801.201233</v>
+        <v>2262617114.379786</v>
       </c>
       <c r="N15">
-        <v>8465814868.773523</v>
+        <v>9178573854.616552</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,13 +447,13 @@
         <v>27886.51173331669</v>
       </c>
       <c r="F2">
-        <v>47998.56044319943</v>
+        <v>287991.3626591965</v>
       </c>
       <c r="G2">
-        <v>41293.01876841089</v>
+        <v>247758.1126104651</v>
       </c>
       <c r="H2">
-        <v>54281.36154998886</v>
+        <v>325688.1692999321</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6383808538.945524</v>
+        <v>38302851233.67314</v>
       </c>
       <c r="M2">
-        <v>5491971496.198648</v>
+        <v>32951828977.19185</v>
       </c>
       <c r="N2">
-        <v>7219421086.148519</v>
+        <v>43316526516.89098</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>38536.21438536532</v>
       </c>
       <c r="F3">
-        <v>53346.97483971681</v>
+        <v>320081.8490383019</v>
       </c>
       <c r="G3">
-        <v>46119.66778995514</v>
+        <v>276718.0067397309</v>
       </c>
       <c r="H3">
-        <v>60125.7675714435</v>
+        <v>360754.6054286612</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,19 +513,19 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>7095147653.682336</v>
+        <v>42570885922.09415</v>
       </c>
       <c r="M3">
-        <v>6133915816.064034</v>
+        <v>36803494896.38421</v>
       </c>
       <c r="N3">
-        <v>7996727087.001986</v>
+        <v>47980362522.01193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,46 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>1248.612815553223</v>
+        <v>18574.73159296868</v>
       </c>
       <c r="D4">
-        <v>61.29332648930076</v>
+        <v>11620.21651129571</v>
       </c>
       <c r="E4">
-        <v>2528.160142138328</v>
+        <v>25438.54197189181</v>
       </c>
       <c r="F4">
-        <v>343.1225477244411</v>
+        <v>18227.96056128219</v>
       </c>
       <c r="G4">
-        <v>12.06727726724682</v>
+        <v>9008.98298610265</v>
       </c>
       <c r="H4">
-        <v>878.8530461058352</v>
+        <v>30294.58102630371</v>
       </c>
       <c r="I4">
-        <v>55047593.19929488</v>
+        <v>1034649699.191539</v>
       </c>
       <c r="J4">
-        <v>2702238.884933811</v>
+        <v>647269300.1121955</v>
       </c>
       <c r="K4">
-        <v>111458996.1864522</v>
+        <v>1416977664.91832</v>
       </c>
       <c r="L4">
-        <v>45635298.84735067</v>
+        <v>2424318754.650531</v>
       </c>
       <c r="M4">
-        <v>1604947.876543826</v>
+        <v>1198194737.151653</v>
       </c>
       <c r="N4">
-        <v>116887455.1320761</v>
+        <v>4029179276.498394</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,46 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>21083.53521120251</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>13511.51035665206</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28536.52674465354</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16049.30625829875</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8044.622459631398</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>26519.2752860746</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1174395078.3344</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>752618149.88623</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1589541612.730696</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2134557732.353734</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1069934787.130976</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3527063613.047921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,46 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>18574.73159296868</v>
+        <v>19639.00221098947</v>
       </c>
       <c r="D6">
-        <v>11620.21651129571</v>
+        <v>945.2686101049807</v>
       </c>
       <c r="E6">
-        <v>25438.54197189181</v>
+        <v>39758.20605733652</v>
       </c>
       <c r="F6">
-        <v>3037.993426880372</v>
+        <v>34999.51625488111</v>
       </c>
       <c r="G6">
-        <v>1501.497164350438</v>
+        <v>1312.171796566891</v>
       </c>
       <c r="H6">
-        <v>5049.096837717301</v>
+        <v>81802.08996450927</v>
       </c>
       <c r="I6">
-        <v>1034649699.191539</v>
+        <v>290794705.7381204</v>
       </c>
       <c r="J6">
-        <v>647269300.1121955</v>
+        <v>13996592.30982444</v>
       </c>
       <c r="K6">
-        <v>1416977664.91832</v>
+        <v>588699757.0909815</v>
       </c>
       <c r="L6">
-        <v>404053125.7750894</v>
+        <v>4654935661.899187</v>
       </c>
       <c r="M6">
-        <v>199699122.8586083</v>
+        <v>174518848.9433964</v>
       </c>
       <c r="N6">
-        <v>671529879.416401</v>
+        <v>10879677965.27973</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -678,46 +678,46 @@
         </is>
       </c>
       <c r="C7">
-        <v>21083.53521120251</v>
+        <v>10911.63767997198</v>
       </c>
       <c r="D7">
-        <v>13511.51035665206</v>
+        <v>460.823121919975</v>
       </c>
       <c r="E7">
-        <v>28536.52674465354</v>
+        <v>22052.50879113228</v>
       </c>
       <c r="F7">
-        <v>2674.884376383136</v>
+        <v>10507.83350574811</v>
       </c>
       <c r="G7">
-        <v>1340.770409938568</v>
+        <v>393.2500430385832</v>
       </c>
       <c r="H7">
-        <v>4419.879214345772</v>
+        <v>24534.90924659295</v>
       </c>
       <c r="I7">
-        <v>1174395078.3344</v>
+        <v>161568619.1273454</v>
       </c>
       <c r="J7">
-        <v>752618149.88623</v>
+        <v>6823407.966269104</v>
       </c>
       <c r="K7">
-        <v>1589541612.730696</v>
+        <v>326531497.6702951</v>
       </c>
       <c r="L7">
-        <v>355759622.0589571</v>
+        <v>1397541856.264498</v>
       </c>
       <c r="M7">
-        <v>178322464.5218296</v>
+        <v>52302255.72413157</v>
       </c>
       <c r="N7">
-        <v>587843935.5079877</v>
+        <v>3263142929.796862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,46 +726,46 @@
         </is>
       </c>
       <c r="C8">
-        <v>19639.00221098947</v>
+        <v>3079.152031990513</v>
       </c>
       <c r="D8">
-        <v>945.2686101049807</v>
+        <v>-81.5652831526404</v>
       </c>
       <c r="E8">
-        <v>39758.20605733652</v>
+        <v>5771.468572331606</v>
       </c>
       <c r="F8">
-        <v>5833.252709146847</v>
+        <v>6408.052173675374</v>
       </c>
       <c r="G8">
-        <v>218.6952994278149</v>
+        <v>-127.5342819378562</v>
       </c>
       <c r="H8">
-        <v>13633.68166075154</v>
+        <v>15253.19523882721</v>
       </c>
       <c r="I8">
-        <v>290794705.7381204</v>
+        <v>231555311.9577184</v>
       </c>
       <c r="J8">
-        <v>13996592.30982444</v>
+        <v>-6133790.858361734</v>
       </c>
       <c r="K8">
-        <v>588699757.0909815</v>
+        <v>434020208.1079093</v>
       </c>
       <c r="L8">
-        <v>775822610.3165307</v>
+        <v>852270939.0988246</v>
       </c>
       <c r="M8">
-        <v>29086474.82389938</v>
+        <v>-16962059.49773488</v>
       </c>
       <c r="N8">
-        <v>1813279660.879955</v>
+        <v>2028674966.764018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -774,46 +774,46 @@
         </is>
       </c>
       <c r="C9">
-        <v>10911.63767997198</v>
+        <v>3415.492903387784</v>
       </c>
       <c r="D9">
-        <v>460.823121919975</v>
+        <v>-87.66933312498075</v>
       </c>
       <c r="E9">
-        <v>22052.50879113228</v>
+        <v>6389.26496163765</v>
       </c>
       <c r="F9">
-        <v>1751.305584291346</v>
+        <v>6139.17200634873</v>
       </c>
       <c r="G9">
-        <v>65.54167383976392</v>
+        <v>-127.3253159773389</v>
       </c>
       <c r="H9">
-        <v>4089.151541098824</v>
+        <v>14631.56693980678</v>
       </c>
       <c r="I9">
-        <v>161568619.1273454</v>
+        <v>256848481.8276645</v>
       </c>
       <c r="J9">
-        <v>6823407.966269104</v>
+        <v>-6592821.520331657</v>
       </c>
       <c r="K9">
-        <v>326531497.6702951</v>
+        <v>480479114.3801115</v>
       </c>
       <c r="L9">
-        <v>232923642.710749</v>
+        <v>816509876.8443811</v>
       </c>
       <c r="M9">
-        <v>8717042.6206886</v>
+        <v>-16934267.02498607</v>
       </c>
       <c r="N9">
-        <v>543857154.9661436</v>
+        <v>1945998402.994302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -822,46 +822,46 @@
         </is>
       </c>
       <c r="C10">
-        <v>3079.152031990513</v>
+        <v>8289.94422304287</v>
       </c>
       <c r="D10">
-        <v>-81.5652831526404</v>
+        <v>6022.233564455917</v>
       </c>
       <c r="E10">
-        <v>5771.468572331606</v>
+        <v>10331.62833484003</v>
       </c>
       <c r="F10">
-        <v>1068.008695612565</v>
+        <v>15290.61964606795</v>
       </c>
       <c r="G10">
-        <v>-21.25571365630943</v>
+        <v>8925.728926396978</v>
       </c>
       <c r="H10">
-        <v>2542.199206471206</v>
+        <v>21658.62276182612</v>
       </c>
       <c r="I10">
-        <v>231555311.9577184</v>
+        <v>139594370.7718183</v>
       </c>
       <c r="J10">
-        <v>-6133790.858361734</v>
+        <v>101408390.9918734</v>
       </c>
       <c r="K10">
-        <v>434020208.1079093</v>
+        <v>173974289.5303712</v>
       </c>
       <c r="L10">
-        <v>142045156.5164712</v>
+        <v>2033652412.927037</v>
       </c>
       <c r="M10">
-        <v>-2827009.916289154</v>
+        <v>1187121947.210798</v>
       </c>
       <c r="N10">
-        <v>338112494.4606704</v>
+        <v>2880596827.322874</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -870,46 +870,46 @@
         </is>
       </c>
       <c r="C11">
-        <v>3415.492903387784</v>
+        <v>5199.494302381868</v>
       </c>
       <c r="D11">
-        <v>-87.66933312498075</v>
+        <v>3806.472494643124</v>
       </c>
       <c r="E11">
-        <v>6389.26496163765</v>
+        <v>6449.432056470911</v>
       </c>
       <c r="F11">
-        <v>1023.195334391456</v>
+        <v>5399.633159346871</v>
       </c>
       <c r="G11">
-        <v>-21.22088599622311</v>
+        <v>3171.963608625719</v>
       </c>
       <c r="H11">
-        <v>2438.594489967799</v>
+        <v>7618.96876310422</v>
       </c>
       <c r="I11">
-        <v>256848481.8276645</v>
+        <v>87554284.55780822</v>
       </c>
       <c r="J11">
-        <v>-6592821.520331657</v>
+        <v>64097190.33729566</v>
       </c>
       <c r="K11">
-        <v>480479114.3801115</v>
+        <v>108601986.3989135</v>
       </c>
       <c r="L11">
-        <v>136084979.4740637</v>
+        <v>718151210.1931338</v>
       </c>
       <c r="M11">
-        <v>-2822377.837497673</v>
+        <v>421871159.9472206</v>
       </c>
       <c r="N11">
-        <v>324333067.1657173</v>
+        <v>1013322845.492861</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -918,46 +918,46 @@
         </is>
       </c>
       <c r="C12">
-        <v>8289.94422304287</v>
+        <v>107153.1553122108</v>
       </c>
       <c r="D12">
-        <v>6022.233564455917</v>
+        <v>79218.0166650977</v>
       </c>
       <c r="E12">
-        <v>10331.62833484003</v>
+        <v>129974.2989825751</v>
       </c>
       <c r="F12">
-        <v>2548.436607677986</v>
+        <v>319829.3050394356</v>
       </c>
       <c r="G12">
-        <v>1487.62148773283</v>
+        <v>146325.7040484844</v>
       </c>
       <c r="H12">
-        <v>3609.770460304351</v>
+        <v>592720.3022994641</v>
       </c>
       <c r="I12">
-        <v>139594370.7718183</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>101408390.9918734</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>173974289.5303712</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>338942068.8211722</v>
+        <v>42537297570.24494</v>
       </c>
       <c r="M12">
-        <v>197853657.8684663</v>
+        <v>19461318638.44842</v>
       </c>
       <c r="N12">
-        <v>480099471.2204787</v>
+        <v>78831800205.82874</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -966,136 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>5199.494302381868</v>
+        <v>44955.61251605048</v>
       </c>
       <c r="D13">
-        <v>3806.472494643124</v>
+        <v>33286.7661588011</v>
       </c>
       <c r="E13">
-        <v>6449.432056470911</v>
+        <v>54504.37393346629</v>
       </c>
       <c r="F13">
-        <v>899.9388598911455</v>
+        <v>111660.4564958147</v>
       </c>
       <c r="G13">
-        <v>528.6606014376198</v>
+        <v>51036.47626420549</v>
       </c>
       <c r="H13">
-        <v>1269.828127184036</v>
+        <v>207035.5004800728</v>
       </c>
       <c r="I13">
-        <v>87554284.55780822</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>64097190.33729566</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>108601986.3989135</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>119691868.3655224</v>
+        <v>14850840713.94335</v>
       </c>
       <c r="M13">
-        <v>70311859.99120343</v>
+        <v>6787851343.139331</v>
       </c>
       <c r="N13">
-        <v>168887140.9154768</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>107153.1553122108</v>
-      </c>
-      <c r="D14">
-        <v>79218.0166650977</v>
-      </c>
-      <c r="E14">
-        <v>129974.2989825751</v>
-      </c>
-      <c r="F14">
-        <v>106609.7683464787</v>
-      </c>
-      <c r="G14">
-        <v>48775.23468282799</v>
-      </c>
-      <c r="H14">
-        <v>197573.4340998212</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>14179099190.08167</v>
-      </c>
-      <c r="M14">
-        <v>6487106212.816123</v>
-      </c>
-      <c r="N14">
-        <v>26277266735.27622</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>44955.61251605048</v>
-      </c>
-      <c r="D15">
-        <v>33286.7661588011</v>
-      </c>
-      <c r="E15">
-        <v>54504.37393346629</v>
-      </c>
-      <c r="F15">
-        <v>37220.15216527147</v>
-      </c>
-      <c r="G15">
-        <v>17012.15875473523</v>
-      </c>
-      <c r="H15">
-        <v>69011.83349335754</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>4950280237.981105</v>
-      </c>
-      <c r="M15">
-        <v>2262617114.379786</v>
-      </c>
-      <c r="N15">
-        <v>9178573854.616552</v>
+        <v>27535721563.84969</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24600.95049746287</v>
+        <v>72284.62766557239</v>
       </c>
       <c r="D2">
-        <v>21089.5996061323</v>
+        <v>48084.4110669566</v>
       </c>
       <c r="E2">
-        <v>27886.51173331669</v>
+        <v>94627.90013825431</v>
       </c>
       <c r="F2">
-        <v>287991.3626591965</v>
+        <v>862722.7836801845</v>
       </c>
       <c r="G2">
-        <v>247758.1126104651</v>
+        <v>573192.0302250907</v>
       </c>
       <c r="H2">
-        <v>325688.1692999321</v>
+        <v>1128350.466164012</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38302851233.67314</v>
+        <v>114742130229.4645</v>
       </c>
       <c r="M2">
-        <v>32951828977.19185</v>
+        <v>76234540019.93706</v>
       </c>
       <c r="N2">
-        <v>43316526516.89098</v>
+        <v>150070611999.8136</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34207.77804873243</v>
+        <v>102046.0169206659</v>
       </c>
       <c r="D3">
-        <v>29593.57874547202</v>
+        <v>68124.49124786434</v>
       </c>
       <c r="E3">
-        <v>38536.21438536532</v>
+        <v>133109.0796819582</v>
       </c>
       <c r="F3">
-        <v>320081.8490383019</v>
+        <v>960283.214914445</v>
       </c>
       <c r="G3">
-        <v>276718.0067397309</v>
+        <v>640089.9770229163</v>
       </c>
       <c r="H3">
-        <v>360754.6054286612</v>
+        <v>1253185.008134241</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42570885922.09415</v>
+        <v>127717667583.6212</v>
       </c>
       <c r="M3">
-        <v>36803494896.38421</v>
+        <v>85131966944.04787</v>
       </c>
       <c r="N3">
-        <v>47980362522.01193</v>
+        <v>166673606081.8541</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18574.73159296868</v>
+        <v>117886.5436723316</v>
       </c>
       <c r="D4">
-        <v>11620.21651129571</v>
+        <v>78284.21539504752</v>
       </c>
       <c r="E4">
-        <v>25438.54197189181</v>
+        <v>154304.8252597238</v>
       </c>
       <c r="F4">
-        <v>18227.96056128219</v>
+        <v>115659.0802036981</v>
       </c>
       <c r="G4">
-        <v>9008.98298610265</v>
+        <v>60245.46088767755</v>
       </c>
       <c r="H4">
-        <v>30294.58102630371</v>
+        <v>184413.4626555989</v>
       </c>
       <c r="I4">
-        <v>1034649699.191539</v>
+        <v>6566516255.636278</v>
       </c>
       <c r="J4">
-        <v>647269300.1121955</v>
+        <v>4360587365.934971</v>
       </c>
       <c r="K4">
-        <v>1416977664.91832</v>
+        <v>8595087376.617168</v>
       </c>
       <c r="L4">
-        <v>2424318754.650531</v>
+        <v>15382657667.09185</v>
       </c>
       <c r="M4">
-        <v>1198194737.151653</v>
+        <v>8012646298.061114</v>
       </c>
       <c r="N4">
-        <v>4029179276.498394</v>
+        <v>24526990533.19465</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21083.53521120251</v>
+        <v>135035.9127274927</v>
       </c>
       <c r="D5">
-        <v>13511.51035665206</v>
+        <v>90022.72424851448</v>
       </c>
       <c r="E5">
-        <v>28536.52674465354</v>
+        <v>176137.8008177906</v>
       </c>
       <c r="F5">
-        <v>16049.30625829875</v>
+        <v>102600.5343959853</v>
       </c>
       <c r="G5">
-        <v>8044.622459631398</v>
+        <v>53643.65289969727</v>
       </c>
       <c r="H5">
-        <v>26519.2752860746</v>
+        <v>163218.2456202052</v>
       </c>
       <c r="I5">
-        <v>1174395078.3344</v>
+        <v>7521770410.746783</v>
       </c>
       <c r="J5">
-        <v>752618149.88623</v>
+        <v>5014445786.090731</v>
       </c>
       <c r="K5">
-        <v>1589541612.730696</v>
+        <v>9811227781.152529</v>
       </c>
       <c r="L5">
-        <v>2134557732.353734</v>
+        <v>13645871074.66604</v>
       </c>
       <c r="M5">
-        <v>1069934787.130976</v>
+        <v>7134605835.659737</v>
       </c>
       <c r="N5">
-        <v>3527063613.047921</v>
+        <v>21708026667.48729</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>19639.00221098947</v>
+        <v>493853.5704780469</v>
       </c>
       <c r="D6">
-        <v>945.2686101049807</v>
+        <v>328226.9507208758</v>
       </c>
       <c r="E6">
-        <v>39758.20605733652</v>
+        <v>645753.0722034946</v>
       </c>
       <c r="F6">
-        <v>34999.51625488111</v>
+        <v>877790.6419214751</v>
       </c>
       <c r="G6">
-        <v>1312.171796566891</v>
+        <v>461701.5622686198</v>
       </c>
       <c r="H6">
-        <v>81802.08996450927</v>
+        <v>1325023.531220962</v>
       </c>
       <c r="I6">
-        <v>290794705.7381204</v>
+        <v>7312489818.068479</v>
       </c>
       <c r="J6">
-        <v>13996592.30982444</v>
+        <v>4860056459.324021</v>
       </c>
       <c r="K6">
-        <v>588699757.0909815</v>
+        <v>9561665740.117142</v>
       </c>
       <c r="L6">
-        <v>4654935661.899187</v>
+        <v>116746155375.5562</v>
       </c>
       <c r="M6">
-        <v>174518848.9433964</v>
+        <v>61406307781.72644</v>
       </c>
       <c r="N6">
-        <v>10879677965.27973</v>
+        <v>176228129652.388</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>10911.63767997198</v>
+        <v>268310.6174033448</v>
       </c>
       <c r="D7">
-        <v>460.823121919975</v>
+        <v>178827.4807946069</v>
       </c>
       <c r="E7">
-        <v>22052.50879113228</v>
+        <v>350082.5690477403</v>
       </c>
       <c r="F7">
-        <v>10507.83350574811</v>
+        <v>262176.4920945704</v>
       </c>
       <c r="G7">
-        <v>393.2500430385832</v>
+        <v>138259.677997432</v>
       </c>
       <c r="H7">
-        <v>24534.90924659295</v>
+        <v>395254.567807476</v>
       </c>
       <c r="I7">
-        <v>161568619.1273454</v>
+        <v>3972875311.891338</v>
       </c>
       <c r="J7">
-        <v>6823407.966269104</v>
+        <v>2647898508.125763</v>
       </c>
       <c r="K7">
-        <v>326531497.6702951</v>
+        <v>5183672599.889918</v>
       </c>
       <c r="L7">
-        <v>1397541856.264498</v>
+        <v>34869473448.57787</v>
       </c>
       <c r="M7">
-        <v>52302255.72413157</v>
+        <v>18388537173.65845</v>
       </c>
       <c r="N7">
-        <v>3263142929.796862</v>
+        <v>52568857518.3943</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3079.152031990513</v>
+        <v>34465.89219477386</v>
       </c>
       <c r="D8">
-        <v>-81.5652831526404</v>
+        <v>22889.33619511552</v>
       </c>
       <c r="E8">
-        <v>5771.468572331606</v>
+        <v>45065.06656815319</v>
       </c>
       <c r="F8">
-        <v>6408.052173675374</v>
+        <v>71849.66141899109</v>
       </c>
       <c r="G8">
-        <v>-127.5342819378562</v>
+        <v>35529.94280500161</v>
       </c>
       <c r="H8">
-        <v>15253.19523882721</v>
+        <v>119257.8196139966</v>
       </c>
       <c r="I8">
-        <v>231555311.9577184</v>
+        <v>2591869558.939158</v>
       </c>
       <c r="J8">
-        <v>-6133790.858361734</v>
+        <v>1721300971.20888</v>
       </c>
       <c r="K8">
-        <v>434020208.1079093</v>
+        <v>3388938070.991676</v>
       </c>
       <c r="L8">
-        <v>852270939.0988246</v>
+        <v>9556004968.725815</v>
       </c>
       <c r="M8">
-        <v>-16962059.49773488</v>
+        <v>4725482393.065215</v>
       </c>
       <c r="N8">
-        <v>2028674966.764018</v>
+        <v>15861290008.66155</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3415.492903387784</v>
+        <v>38037.68714566478</v>
       </c>
       <c r="D9">
-        <v>-87.66933312498075</v>
+        <v>25352.85630764702</v>
       </c>
       <c r="E9">
-        <v>6389.26496163765</v>
+        <v>49653.47049522461</v>
       </c>
       <c r="F9">
-        <v>6139.17200634873</v>
+        <v>69441.81173547711</v>
       </c>
       <c r="G9">
-        <v>-127.3253159773389</v>
+        <v>34466.93513057644</v>
       </c>
       <c r="H9">
-        <v>14631.56693980678</v>
+        <v>115138.653168651</v>
       </c>
       <c r="I9">
-        <v>256848481.8276645</v>
+        <v>2860472111.041142</v>
       </c>
       <c r="J9">
-        <v>-6592821.520331657</v>
+        <v>1906560147.191354</v>
       </c>
       <c r="K9">
-        <v>480479114.3801115</v>
+        <v>3733990634.711379</v>
       </c>
       <c r="L9">
-        <v>816509876.8443811</v>
+        <v>9235760960.818455</v>
       </c>
       <c r="M9">
-        <v>-16934267.02498607</v>
+        <v>4584102372.366666</v>
       </c>
       <c r="N9">
-        <v>1945998402.994302</v>
+        <v>15313440871.43058</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8289.94422304287</v>
+        <v>34578.19430233459</v>
       </c>
       <c r="D10">
-        <v>6022.233564455917</v>
+        <v>22976.43108481871</v>
       </c>
       <c r="E10">
-        <v>10331.62833484003</v>
+        <v>45290.09011992066</v>
       </c>
       <c r="F10">
-        <v>15290.61964606795</v>
+        <v>63821.90412607118</v>
       </c>
       <c r="G10">
-        <v>8925.728926396978</v>
+        <v>33947.24246429134</v>
       </c>
       <c r="H10">
-        <v>21658.62276182612</v>
+        <v>95135.70951498931</v>
       </c>
       <c r="I10">
-        <v>139594370.7718183</v>
+        <v>582262213.8570119</v>
       </c>
       <c r="J10">
-        <v>101408390.9918734</v>
+        <v>386900123.0372596</v>
       </c>
       <c r="K10">
-        <v>173974289.5303712</v>
+        <v>762639827.5293336</v>
       </c>
       <c r="L10">
-        <v>2033652412.927037</v>
+        <v>8488313248.767467</v>
       </c>
       <c r="M10">
-        <v>1187121947.210798</v>
+        <v>4514983247.750748</v>
       </c>
       <c r="N10">
-        <v>2880596827.322874</v>
+        <v>12653049365.49358</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5199.494302381868</v>
+        <v>22179.61976357391</v>
       </c>
       <c r="D11">
-        <v>3806.472494643124</v>
+        <v>14812.73631561984</v>
       </c>
       <c r="E11">
-        <v>6449.432056470911</v>
+        <v>28924.54663747968</v>
       </c>
       <c r="F11">
-        <v>5399.633159346871</v>
+        <v>22945.96982162615</v>
       </c>
       <c r="G11">
-        <v>3171.963608625719</v>
+        <v>12259.37490255628</v>
       </c>
       <c r="H11">
-        <v>7618.96876310422</v>
+        <v>34083.43398095013</v>
       </c>
       <c r="I11">
-        <v>87554284.55780822</v>
+        <v>373482617.198818</v>
       </c>
       <c r="J11">
-        <v>64097190.33729566</v>
+        <v>249431666.8187215</v>
       </c>
       <c r="K11">
-        <v>108601986.3989135</v>
+        <v>487060440.8285231</v>
       </c>
       <c r="L11">
-        <v>718151210.1931338</v>
+        <v>3051813986.276278</v>
       </c>
       <c r="M11">
-        <v>421871159.9472206</v>
+        <v>1630496862.039985</v>
       </c>
       <c r="N11">
-        <v>1013322845.492861</v>
+        <v>4533096719.466367</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107153.1553122108</v>
+        <v>757338.2337135491</v>
       </c>
       <c r="D12">
-        <v>79218.0166650977</v>
+        <v>503307.8258941504</v>
       </c>
       <c r="E12">
-        <v>129974.2989825751</v>
+        <v>990407.5383711181</v>
       </c>
       <c r="F12">
-        <v>319829.3050394356</v>
+        <v>2256046.518983672</v>
       </c>
       <c r="G12">
-        <v>146325.7040484844</v>
+        <v>927611.059660397</v>
       </c>
       <c r="H12">
-        <v>592720.3022994641</v>
+        <v>4507562.785151743</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>42537297570.24494</v>
+        <v>300054187024.8284</v>
       </c>
       <c r="M12">
-        <v>19461318638.44842</v>
+        <v>123372270934.8328</v>
       </c>
       <c r="N12">
-        <v>78831800205.82874</v>
+        <v>599505850425.1819</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44955.61251605048</v>
+        <v>316394.7589704457</v>
       </c>
       <c r="D13">
-        <v>33286.7661588011</v>
+        <v>210975.1801000892</v>
       </c>
       <c r="E13">
-        <v>54504.37393346629</v>
+        <v>413107.0182192521</v>
       </c>
       <c r="F13">
-        <v>111660.4564958147</v>
+        <v>794459.7810503439</v>
       </c>
       <c r="G13">
-        <v>51036.47626420549</v>
+        <v>327638.2462736432</v>
       </c>
       <c r="H13">
-        <v>207035.5004800728</v>
+        <v>1586199.486621887</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>14850840713.94335</v>
+        <v>105663150879.6957</v>
       </c>
       <c r="M13">
-        <v>6787851343.139331</v>
+        <v>43575886754.39455</v>
       </c>
       <c r="N13">
-        <v>27535721563.84969</v>
+        <v>210964531720.711</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_sex.xlsx
+++ b/output/Tables/2019/cases_prev_2019_sex.xlsx
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,46 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>117886.5436723316</v>
+        <v>493853.5704780469</v>
       </c>
       <c r="D4">
-        <v>78284.21539504752</v>
+        <v>328226.9507208758</v>
       </c>
       <c r="E4">
-        <v>154304.8252597238</v>
+        <v>645753.0722034946</v>
       </c>
       <c r="F4">
-        <v>115659.0802036981</v>
+        <v>877790.6419214751</v>
       </c>
       <c r="G4">
-        <v>60245.46088767755</v>
+        <v>461701.5622686198</v>
       </c>
       <c r="H4">
-        <v>184413.4626555989</v>
+        <v>1325023.531220962</v>
       </c>
       <c r="I4">
-        <v>6566516255.636278</v>
+        <v>7312489818.068479</v>
       </c>
       <c r="J4">
-        <v>4360587365.934971</v>
+        <v>4860056459.324021</v>
       </c>
       <c r="K4">
-        <v>8595087376.617168</v>
+        <v>9561665740.117142</v>
       </c>
       <c r="L4">
-        <v>15382657667.09185</v>
+        <v>116746155375.5562</v>
       </c>
       <c r="M4">
-        <v>8012646298.061114</v>
+        <v>61406307781.72644</v>
       </c>
       <c r="N4">
-        <v>24526990533.19465</v>
+        <v>176228129652.388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,46 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>135035.9127274927</v>
+        <v>268310.6174033448</v>
       </c>
       <c r="D5">
-        <v>90022.72424851448</v>
+        <v>178827.4807946069</v>
       </c>
       <c r="E5">
-        <v>176137.8008177906</v>
+        <v>350082.5690477403</v>
       </c>
       <c r="F5">
-        <v>102600.5343959853</v>
+        <v>262176.4920945704</v>
       </c>
       <c r="G5">
-        <v>53643.65289969727</v>
+        <v>138259.677997432</v>
       </c>
       <c r="H5">
-        <v>163218.2456202052</v>
+        <v>395254.567807476</v>
       </c>
       <c r="I5">
-        <v>7521770410.746783</v>
+        <v>3972875311.891338</v>
       </c>
       <c r="J5">
-        <v>5014445786.090731</v>
+        <v>2647898508.125763</v>
       </c>
       <c r="K5">
-        <v>9811227781.152529</v>
+        <v>5183672599.889918</v>
       </c>
       <c r="L5">
-        <v>13645871074.66604</v>
+        <v>34869473448.57787</v>
       </c>
       <c r="M5">
-        <v>7134605835.659737</v>
+        <v>18388537173.65845</v>
       </c>
       <c r="N5">
-        <v>21708026667.48729</v>
+        <v>52568857518.3943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,46 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>493853.5704780469</v>
+        <v>117886.5436723316</v>
       </c>
       <c r="D6">
-        <v>328226.9507208758</v>
+        <v>78284.21539504752</v>
       </c>
       <c r="E6">
-        <v>645753.0722034946</v>
+        <v>154304.8252597238</v>
       </c>
       <c r="F6">
-        <v>877790.6419214751</v>
+        <v>115659.0802036981</v>
       </c>
       <c r="G6">
-        <v>461701.5622686198</v>
+        <v>60245.46088767755</v>
       </c>
       <c r="H6">
-        <v>1325023.531220962</v>
+        <v>184413.4626555989</v>
       </c>
       <c r="I6">
-        <v>7312489818.068479</v>
+        <v>6566516255.636278</v>
       </c>
       <c r="J6">
-        <v>4860056459.324021</v>
+        <v>4360587365.934971</v>
       </c>
       <c r="K6">
-        <v>9561665740.117142</v>
+        <v>8595087376.617168</v>
       </c>
       <c r="L6">
-        <v>116746155375.5562</v>
+        <v>15382657667.09185</v>
       </c>
       <c r="M6">
-        <v>61406307781.72644</v>
+        <v>8012646298.061114</v>
       </c>
       <c r="N6">
-        <v>176228129652.388</v>
+        <v>24526990533.19465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>268310.6174033448</v>
+        <v>135035.9127274927</v>
       </c>
       <c r="D7">
-        <v>178827.4807946069</v>
+        <v>90022.72424851448</v>
       </c>
       <c r="E7">
-        <v>350082.5690477403</v>
+        <v>176137.8008177906</v>
       </c>
       <c r="F7">
-        <v>262176.4920945704</v>
+        <v>102600.5343959853</v>
       </c>
       <c r="G7">
-        <v>138259.677997432</v>
+        <v>53643.65289969727</v>
       </c>
       <c r="H7">
-        <v>395254.567807476</v>
+        <v>163218.2456202052</v>
       </c>
       <c r="I7">
-        <v>3972875311.891338</v>
+        <v>7521770410.746783</v>
       </c>
       <c r="J7">
-        <v>2647898508.125763</v>
+        <v>5014445786.090731</v>
       </c>
       <c r="K7">
-        <v>5183672599.889918</v>
+        <v>9811227781.152529</v>
       </c>
       <c r="L7">
-        <v>34869473448.57787</v>
+        <v>13645871074.66604</v>
       </c>
       <c r="M7">
-        <v>18388537173.65845</v>
+        <v>7134605835.659737</v>
       </c>
       <c r="N7">
-        <v>52568857518.3943</v>
+        <v>21708026667.48729</v>
       </c>
     </row>
     <row r="8">
